--- a/TestData/LV_TMTC0033975_VerifyFunctionalityOfCompaniesInfo.xlsx
+++ b/TestData/LV_TMTC0033975_VerifyFunctionalityOfCompaniesInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE1325B-7350-45C5-BF3C-B5AFAA129341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76355676-F094-49D3-AE0E-81439A403D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>CompanyType</t>
   </si>
@@ -246,15 +246,9 @@
     <t>PhoneNumber</t>
   </si>
   <si>
-    <t>(123) 456-7890</t>
-  </si>
-  <si>
     <t>NewPhoneNumber</t>
   </si>
   <si>
-    <t>(223) 456-7890</t>
-  </si>
-  <si>
     <t>TestOperatingCompanyInfo</t>
   </si>
   <si>
@@ -277,6 +271,18 @@
   </si>
   <si>
     <t>Round Trip</t>
+  </si>
+  <si>
+    <t>(773) 456-7890</t>
+  </si>
+  <si>
+    <t>(993) 456-7850</t>
+  </si>
+  <si>
+    <t>(593) 456-7850</t>
+  </si>
+  <si>
+    <t>(873) 456-7890</t>
   </si>
 </sst>
 </file>
@@ -667,7 +673,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -837,7 +843,7 @@
         <v>65</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -845,13 +851,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -881,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
         <v>45</v>
@@ -890,10 +896,10 @@
         <v>48</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -901,13 +907,13 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1020,13 +1026,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1075,13 +1081,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/TestData/LV_TMTC0033975_VerifyFunctionalityOfCompaniesInfo.xlsx
+++ b/TestData/LV_TMTC0033975_VerifyFunctionalityOfCompaniesInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76355676-F094-49D3-AE0E-81439A403D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652C667E-AD36-4076-975E-88861236572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
